--- a/main/ig/StructureDefinition-fr-service-request-document.xlsx
+++ b/main/ig/StructureDefinition-fr-service-request-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T11:53:23+00:00</t>
+    <t>2026-09-18T08:26:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-service-request-document.xlsx
+++ b/main/ig/StructureDefinition-fr-service-request-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T08:26:19+00:00</t>
+    <t>2026-09-24T07:33:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-service-request-document.xlsx
+++ b/main/ig/StructureDefinition-fr-service-request-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-24T07:33:45+00:00</t>
+    <t>2026-09-30T20:06:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-service-request-document.xlsx
+++ b/main/ig/StructureDefinition-fr-service-request-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T20:06:50+00:00</t>
+    <t>2026-10-01T08:49:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-service-request-document.xlsx
+++ b/main/ig/StructureDefinition-fr-service-request-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T08:49:37+00:00</t>
+    <t>2026-10-01T13:34:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-service-request-document.xlsx
+++ b/main/ig/StructureDefinition-fr-service-request-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T13:34:48+00:00</t>
+    <t>2026-10-05T07:58:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
